--- a/CMport_问卷星导入_Day3.xlsx
+++ b/CMport_问卷星导入_Day3.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="试题" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,30 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,32 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,524 +413,381 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>题型</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>题干</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>选项A</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>选项B</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>选项C</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>选项D</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>选项E</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>选项F</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>正确答案</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>分值</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>答案解析</t>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>解析</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>"一国两制"方针的核心意义在于？</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>保留香港原有的独立政治体制</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>解决历史遗留问题、实现国家统一，同时保持香港长期繁荣稳定</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>让香港完全独立于国家体制之外运作</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>主要目的是保障外商在港投资权益</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《香港特别行政区基本法》序言；邓小平系列讲话
-"一国两制"是解决历史遗留问题的伟大创举，既维护国家主权统一，又最大限度保持香港繁荣稳定，开创了国际先例。</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>【依据】《香港特别行政区基本法》序言；邓小平系列讲话 "一国两制"是解决历史遗留问题的伟大创举，既维护国家主权统一，又最大限度保持香港繁荣稳定，开创了国际先例。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>国务院正式印发《粤港澳大湾区发展规划纲要》的年份是？</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2017年</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2018年</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2019年</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2021年</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》（2019年2月18日发布）
-2019年2月18日，国务院正式印发《粤港澳大湾区发展规划纲要》，标志大湾区建设进入全面实施阶段。</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>【依据】《粤港澳大湾区发展规划纲要》（2019年2月18日发布） 2019年2月18日，国务院正式印发《粤港澳大湾区发展规划纲要》，标志大湾区建设进入全面实施阶段。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>《粤港澳大湾区发展规划纲要》中，香港被定位为哪类核心引擎城市？</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>国家先进制造业中心</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>国际金融、航运、贸易中心及国际航空枢纽</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>国家现代农业示范区</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>国家综合交通枢纽</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》第四章
-规划纲要将香港定位为巩固和提升国际金融、航运、贸易中心地位，并强化国际航空枢纽功能，发挥引领带动作用。</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>【依据】《粤港澳大湾区发展规划纲要》第四章 规划纲要将香港定位为巩固和提升国际金融、航运、贸易中心地位，并强化国际航空枢纽功能，发挥引领带动作用。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2022年7月1日，习近平主席出席香港回归祖国25周年庆典，其重要讲话中着重强调的核心原则是？</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>加快香港与内地法律制度完全统一</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>坚持"爱国者治港"，确保"一国两制"行稳致远</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>尽快推动香港重点发展制造业</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>取消香港独立关税区地位</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>【依据】习近平2022年7月1日在庆祝香港回归祖国25周年大会上的重要讲话
-习近平主席强调，"爱国者治港"是保证"一国两制"正确贯彻执行的根本保障，必须长期坚持，确保"一国两制"行稳致远。</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>【依据】习近平2022年7月1日在庆祝香港回归祖国25周年大会上的重要讲话 习近平主席强调，"爱国者治港"是保证"一国两制"正确贯彻执行的根本保障，必须长期坚持，确保"一国两制"行稳致远。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>多选题</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>《粤港澳大湾区发展规划纲要》确立的主要战略目标包括哪些？（多选）</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>《粤港澳大湾区发展规划纲要》确立的主要战略目标包括哪些？（多选）[多选题]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>建设国际科技创新中心</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>构建现代化基础设施体系，提升互联互通水平</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>打造宜居宜业宜游的优质生活圈</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>建立高水平对外开放新体制</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》第三章
-规划纲要确立了科技创新、基础设施、宜居生活及对外开放四大核心目标，涵盖大湾区建设全局。</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>【依据】《粤港澳大湾区发展规划纲要》第三章 规划纲要确立了科技创新、基础设施、宜居生活及对外开放四大核心目标，涵盖大湾区建设全局。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>多选题</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>回归以来，香港在以下哪些方面为国家发展作出了重要贡献？（多选）</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>回归以来，香港在以下哪些方面为国家发展作出了重要贡献？（多选）[多选题]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>作为国际金融中心，长期为国家引进外资、支持内地企业赴港上市融资</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>发挥"超级联系人"作用，连接内地与国际市场</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>积极参与"一带一路"建设，助力国家对外开放</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>独立开展国家航天飞行器研发项目</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>【依据】历次政府工作报告；权威媒体报道
-香港以国际金融中心、超级联系人、"一带一路"重要节点三大角色，为国家高水平开放和经济发展持续发挥独特作用。</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>【依据】历次政府工作报告；权威媒体报道 香港以国际金融中心、超级联系人、"一带一路"重要节点三大角色，为国家高水平开放和经济发展持续发挥独特作用。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>多选题</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>以下哪些重大举措有力推动了香港与内地的互联互通？（多选）</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>以下哪些重大举措有力推动了香港与内地的互联互通？（多选）[多选题]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>广深港高铁全线开通（2018年）</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>港珠澳大桥建成通车（2018年）</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>河套深港科技创新合作区建设</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>粤港澳大湾区个人所得税优惠补贴政策</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>【依据】国家及特区政府官方公告；《粤港澳大湾区发展规划纲要》
-上述举措涵盖交通基础设施、科技创新、人才政策等维度，全面推进大湾区互联互通与深度融合发展。</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>【依据】国家及特区政府官方公告；《粤港澳大湾区发展规划纲要》 上述举措涵盖交通基础设施、科技创新、人才政策等维度，全面推进大湾区互联互通与深度融合发展。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>多选题</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>香港回归祖国的历史意义包括哪些方面？（多选）</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>香港回归祖国的历史意义包括哪些方面？（多选）[多选题]</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>洗雪了中华民族百年屈辱，标志着中国完全恢复对香港行使主权</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>是"一国两制"科学构想的成功实践，证明了其可行性</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>为解决国际历史遗留问题提供了创造性的中国方案</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>极大增强了中华民族的凝聚力、自尊心和民族自信心</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《香港特别行政区基本法》序言；习近平系列讲话
-香港回归是中华民族发展史上的里程碑，以上四方面均是官方文件和学术界高度认可的历史评价。</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>【依据】《香港特别行政区基本法》序言；习近平系列讲话 香港回归是中华民族发展史上的里程碑，以上四方面均是官方文件和学术界高度认可的历史评价。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>多项填空</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>粤港澳大湾区由香港、澳门两个特别行政区和广东省{9}个城市共同组成，通称"{9+2}"。</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>9;9+2</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》
-9个广东城市为：广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆，加上港澳两个特区，合称"9+2"。</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>【依据】《粤港澳大湾区发展规划纲要》 9个广东城市为：广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆，加上港澳两个特区，合称"9+2"。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>多项填空</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026年是香港回归祖国第{29}周年。香港回归是"{一国两制}"伟大构想的成功实践，开创了用和平方式解决历史遗留问题的新范例。</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>29;一国两制</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>【依据】历史记录；《香港特别行政区基本法》序言
-香港于1997年回归，2026年为回归29周年；"一国两制"由邓小平提出，在香港的成功实践为国际社会解决类似问题提供了重要借鉴。</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>【依据】历史记录；《香港特别行政区基本法》序言 香港于1997年回归，2026年为回归29周年；"一国两制"由邓小平提出，在香港的成功实践为国际社会解决类似问题提供了重要借鉴。</t>
         </is>
       </c>
     </row>

--- a/CMport_问卷星导入_Day3.xlsx
+++ b/CMport_问卷星导入_Day3.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>"一国两制"方针的核心意义在于？</t>
+          <t>一国两制方针的核心意义在于？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>【依据】《香港特别行政区基本法》序言；邓小平系列讲话 "一国两制"是解决历史遗留问题的伟大创举，既维护国家主权统一，又最大限度保持香港繁荣稳定，开创了国际先例。</t>
+          <t>依据：《香港特别行政区基本法》序言；邓小平系列讲话。一国两制是解决历史遗留问题的伟大创举，既维护国家主权统一，又最大限度保持香港繁荣稳定，开创了国际先例。</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》（2019年2月18日发布） 2019年2月18日，国务院正式印发《粤港澳大湾区发展规划纲要》，标志大湾区建设进入全面实施阶段。</t>
+          <t>依据：《粤港澳大湾区发展规划纲要》（2019年2月18日发布）。2019年2月18日，国务院正式印发《粤港澳大湾区发展规划纲要》，标志大湾区建设进入全面实施阶段。</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》第四章 规划纲要将香港定位为巩固和提升国际金融、航运、贸易中心地位，并强化国际航空枢纽功能，发挥引领带动作用。</t>
+          <t>依据：《粤港澳大湾区发展规划纲要》第四章。规划纲要将香港定位为巩固和提升国际金融、航运、贸易中心地位，并强化国际航空枢纽功能，发挥引领带动作用。</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>坚持"爱国者治港"，确保"一国两制"行稳致远</t>
+          <t>坚持爱国者治港，确保一国两制行稳致远</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -597,14 +597,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>【依据】习近平2022年7月1日在庆祝香港回归祖国25周年大会上的重要讲话 习近平主席强调，"爱国者治港"是保证"一国两制"正确贯彻执行的根本保障，必须长期坚持，确保"一国两制"行稳致远。</t>
+          <t>依据：习近平2022年7月1日在庆祝香港回归祖国25周年大会上的重要讲话。习近平主席强调，爱国者治港是保证一国两制正确贯彻执行的根本保障，必须长期坚持，确保一国两制行稳致远。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>《粤港澳大湾区发展规划纲要》确立的主要战略目标包括哪些？（多选）[多选题]</t>
+          <t>《粤港澳大湾区发展规划纲要》确立的主要战略目标包括哪些？(ABCD)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -634,14 +634,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》第三章 规划纲要确立了科技创新、基础设施、宜居生活及对外开放四大核心目标，涵盖大湾区建设全局。</t>
+          <t>依据：《粤港澳大湾区发展规划纲要》第三章。规划纲要确立了科技创新、基础设施、宜居生活及对外开放四大核心目标，涵盖大湾区建设全局。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>回归以来，香港在以下哪些方面为国家发展作出了重要贡献？（多选）[多选题]</t>
+          <t>回归以来，香港在以下哪些方面为国家发展作出了重要贡献？(ABC)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>发挥"超级联系人"作用，连接内地与国际市场</t>
+          <t>发挥超级联系人作用，连接内地与国际市场</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>积极参与"一带一路"建设，助力国家对外开放</t>
+          <t>积极参与一带一路建设，助力国家对外开放</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>【依据】历次政府工作报告；权威媒体报道 香港以国际金融中心、超级联系人、"一带一路"重要节点三大角色，为国家高水平开放和经济发展持续发挥独特作用。</t>
+          <t>依据：历次政府工作报告；权威媒体报道。香港以国际金融中心、超级联系人、一带一路重要节点三大角色，为国家高水平开放和经济发展持续发挥独特作用。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>以下哪些重大举措有力推动了香港与内地的互联互通？（多选）[多选题]</t>
+          <t>以下哪些重大举措有力推动了香港与内地的互联互通？(ABCD)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>【依据】国家及特区政府官方公告；《粤港澳大湾区发展规划纲要》 上述举措涵盖交通基础设施、科技创新、人才政策等维度，全面推进大湾区互联互通与深度融合发展。</t>
+          <t>依据：国家及特区政府官方公告；《粤港澳大湾区发展规划纲要》。上述举措涵盖交通基础设施、科技创新、人才政策等维度，全面推进大湾区互联互通与深度融合发展。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>香港回归祖国的历史意义包括哪些方面？（多选）[多选题]</t>
+          <t>香港回归祖国的历史意义包括哪些方面？(ABCD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>是"一国两制"科学构想的成功实践，证明了其可行性</t>
+          <t>是一国两制科学构想的成功实践，证明了其可行性</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -745,14 +745,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>【依据】《香港特别行政区基本法》序言；习近平系列讲话 香港回归是中华民族发展史上的里程碑，以上四方面均是官方文件和学术界高度认可的历史评价。</t>
+          <t>依据：《香港特别行政区基本法》序言；习近平系列讲话。香港回归是中华民族发展史上的里程碑，以上四方面均是官方文件和学术界高度认可的历史评价。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>粤港澳大湾区由香港、澳门两个特别行政区和广东省{9}个城市共同组成，通称"{9+2}"。</t>
+          <t>粤港澳大湾区由香港、澳门两个特别行政区和广东省{9}个城市共同组成，通称{9+2}。</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -766,14 +766,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》 9个广东城市为：广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆，加上港澳两个特区，合称"9+2"。</t>
+          <t>依据：《粤港澳大湾区发展规划纲要》。9个广东城市为：广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆，加上港澳两个特区，合称9+2。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026年是香港回归祖国第{29}周年。香港回归是"{一国两制}"伟大构想的成功实践，开创了用和平方式解决历史遗留问题的新范例。</t>
+          <t>2026年是香港回归祖国第{29}周年。香港回归是{一国两制}伟大构想的成功实践，开创了用和平方式解决历史遗留问题的新范例。</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>【依据】历史记录；《香港特别行政区基本法》序言 香港于1997年回归，2026年为回归29周年；"一国两制"由邓小平提出，在香港的成功实践为国际社会解决类似问题提供了重要借鉴。</t>
+          <t>依据：历史记录；《香港特别行政区基本法》序言。香港于1997年回归，2026年为回归29周年；一国两制由邓小平提出，在香港的成功实践为国际社会解决类似问题提供了重要借鉴。</t>
         </is>
       </c>
     </row>

--- a/CMport_问卷星导入_Day3.xlsx
+++ b/CMport_问卷星导入_Day3.xlsx
@@ -413,8 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -422,372 +425,74 @@
           <t>题干</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>选项A</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>选项B</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>选项C</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>选项D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>正确答案</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>解析</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>一国两制方针的核心意义在于？</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>保留香港原有的独立政治体制</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>解决历史遗留问题、实现国家统一，同时保持香港长期繁荣稳定</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>让香港完全独立于国家体制之外运作</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>主要目的是保障外商在港投资权益</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>依据：《香港特别行政区基本法》序言；邓小平系列讲话。一国两制是解决历史遗留问题的伟大创举，既维护国家主权统一，又最大限度保持香港繁荣稳定，开创了国际先例。</t>
+          <t>1. 一国两制方针的核心意义在于？&lt;br/&gt;&lt;br/&gt;A. 保留香港原有的独立政治体制&lt;br/&gt;B. 解决历史遗留问题、实现国家统一，同时保持香港长期繁荣稳定&lt;br/&gt;C. 让香港完全独立于国家体制之外运作&lt;br/&gt;D. 主要目的是保障外商在港投资权益&lt;br/&gt;&lt;br/&gt;答案：B</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>国务院正式印发《粤港澳大湾区发展规划纲要》的年份是？</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2017年</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2018年</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2019年</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2021年</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>依据：《粤港澳大湾区发展规划纲要》（2019年2月18日发布）。2019年2月18日，国务院正式印发《粤港澳大湾区发展规划纲要》，标志大湾区建设进入全面实施阶段。</t>
+          <t>2. 国务院正式印发《粤港澳大湾区发展规划纲要》的年份是？&lt;br/&gt;&lt;br/&gt;A. 2017年&lt;br/&gt;B. 2018年&lt;br/&gt;C. 2019年&lt;br/&gt;D. 2021年&lt;br/&gt;&lt;br/&gt;答案：C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>《粤港澳大湾区发展规划纲要》中，香港被定位为哪类核心引擎城市？</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>国家先进制造业中心</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>国际金融、航运、贸易中心及国际航空枢纽</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>国家现代农业示范区</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>国家综合交通枢纽</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>依据：《粤港澳大湾区发展规划纲要》第四章。规划纲要将香港定位为巩固和提升国际金融、航运、贸易中心地位，并强化国际航空枢纽功能，发挥引领带动作用。</t>
+          <t>3. 《粤港澳大湾区发展规划纲要》中，香港被定位为哪类核心引擎城市？&lt;br/&gt;&lt;br/&gt;A. 国家先进制造业中心&lt;br/&gt;B. 国际金融、航运、贸易中心及国际航空枢纽&lt;br/&gt;C. 国家现代农业示范区&lt;br/&gt;D. 国家综合交通枢纽&lt;br/&gt;&lt;br/&gt;答案：B</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022年7月1日，习近平主席出席香港回归祖国25周年庆典，其重要讲话中着重强调的核心原则是？</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>加快香港与内地法律制度完全统一</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>坚持爱国者治港，确保一国两制行稳致远</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>尽快推动香港重点发展制造业</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>取消香港独立关税区地位</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>依据：习近平2022年7月1日在庆祝香港回归祖国25周年大会上的重要讲话。习近平主席强调，爱国者治港是保证一国两制正确贯彻执行的根本保障，必须长期坚持，确保一国两制行稳致远。</t>
+          <t>4. 2022年7月1日，习近平主席出席香港回归祖国25周年庆典，其重要讲话中着重强调的核心原则是？&lt;br/&gt;&lt;br/&gt;A. 加快香港与内地法律制度完全统一&lt;br/&gt;B. 坚持爱国者治港，确保一国两制行稳致远&lt;br/&gt;C. 尽快推动香港重点发展制造业&lt;br/&gt;D. 取消香港独立关税区地位&lt;br/&gt;&lt;br/&gt;答案：B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>《粤港澳大湾区发展规划纲要》确立的主要战略目标包括哪些？(ABCD)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>建设国际科技创新中心</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>构建现代化基础设施体系，提升互联互通水平</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>打造宜居宜业宜游的优质生活圈</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>建立高水平对外开放新体制</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ABCD</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>依据：《粤港澳大湾区发展规划纲要》第三章。规划纲要确立了科技创新、基础设施、宜居生活及对外开放四大核心目标，涵盖大湾区建设全局。</t>
+          <t>5. 《粤港澳大湾区发展规划纲要》确立的主要战略目标包括哪些（ ）&lt;br/&gt;&lt;br/&gt;A. 建设国际科技创新中心&lt;br/&gt;B. 构建现代化基础设施体系，提升互联互通水平&lt;br/&gt;C. 打造宜居宜业宜游的优质生活圈&lt;br/&gt;D. 建立高水平对外开放新体制&lt;br/&gt;&lt;br/&gt;答案：ABCD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>回归以来，香港在以下哪些方面为国家发展作出了重要贡献？(ABC)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>作为国际金融中心，长期为国家引进外资、支持内地企业赴港上市融资</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>发挥超级联系人作用，连接内地与国际市场</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>积极参与一带一路建设，助力国家对外开放</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>独立开展国家航天飞行器研发项目</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>依据：历次政府工作报告；权威媒体报道。香港以国际金融中心、超级联系人、一带一路重要节点三大角色，为国家高水平开放和经济发展持续发挥独特作用。</t>
+          <t>6. 回归以来，香港在以下哪些方面为国家发展作出了重要贡献（ ）&lt;br/&gt;&lt;br/&gt;A. 作为国际金融中心，长期为国家引进外资、支持内地企业赴港上市融资&lt;br/&gt;B. 发挥超级联系人作用，连接内地与国际市场&lt;br/&gt;C. 积极参与一带一路建设，助力国家对外开放&lt;br/&gt;D. 独立开展国家航天飞行器研发项目&lt;br/&gt;&lt;br/&gt;答案：ABC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>以下哪些重大举措有力推动了香港与内地的互联互通？(ABCD)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>广深港高铁全线开通（2018年）</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>港珠澳大桥建成通车（2018年）</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>河套深港科技创新合作区建设</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>粤港澳大湾区个人所得税优惠补贴政策</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ABCD</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>依据：国家及特区政府官方公告；《粤港澳大湾区发展规划纲要》。上述举措涵盖交通基础设施、科技创新、人才政策等维度，全面推进大湾区互联互通与深度融合发展。</t>
+          <t>7. 以下哪些重大举措有力推动了香港与内地的互联互通（ ）&lt;br/&gt;&lt;br/&gt;A. 广深港高铁全线开通（2018年）&lt;br/&gt;B. 港珠澳大桥建成通车（2018年）&lt;br/&gt;C. 河套深港科技创新合作区建设&lt;br/&gt;D. 粤港澳大湾区个人所得税优惠补贴政策&lt;br/&gt;&lt;br/&gt;答案：ABCD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>香港回归祖国的历史意义包括哪些方面？(ABCD)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>洗雪了中华民族百年屈辱，标志着中国完全恢复对香港行使主权</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>是一国两制科学构想的成功实践，证明了其可行性</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>为解决国际历史遗留问题提供了创造性的中国方案</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>极大增强了中华民族的凝聚力、自尊心和民族自信心</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ABCD</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>依据：《香港特别行政区基本法》序言；习近平系列讲话。香港回归是中华民族发展史上的里程碑，以上四方面均是官方文件和学术界高度认可的历史评价。</t>
+          <t>8. 香港回归祖国的历史意义包括哪些方面（ ）&lt;br/&gt;&lt;br/&gt;A. 洗雪了中华民族百年屈辱，标志着中国完全恢复对香港行使主权&lt;br/&gt;B. 是一国两制科学构想的成功实践，证明了其可行性&lt;br/&gt;C. 为解决国际历史遗留问题提供了创造性的中国方案&lt;br/&gt;D. 极大增强了中华民族的凝聚力、自尊心和民族自信心&lt;br/&gt;&lt;br/&gt;答案：ABCD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>粤港澳大湾区由香港、澳门两个特别行政区和广东省{9}个城市共同组成，通称{9+2}。</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>9;9+2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>依据：《粤港澳大湾区发展规划纲要》。9个广东城市为：广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆，加上港澳两个特区，合称9+2。</t>
+          <t>9. 粤港澳大湾区由香港、澳门两个特别行政区和广东省____个城市共同组成，通称____。&lt;br/&gt;&lt;br/&gt;答案：9；9+2&lt;br/&gt;&lt;br/&gt;解析：依据：《粤港澳大湾区发展规划纲要》。9个广东城市为：广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆，加上港澳两个特区，合称9+2。&lt;br/&gt;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026年是香港回归祖国第{29}周年。香港回归是{一国两制}伟大构想的成功实践，开创了用和平方式解决历史遗留问题的新范例。</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>29;一国两制</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>依据：历史记录；《香港特别行政区基本法》序言。香港于1997年回归，2026年为回归29周年；一国两制由邓小平提出，在香港的成功实践为国际社会解决类似问题提供了重要借鉴。</t>
+          <t>10. 2026年是香港回归祖国第____周年。香港回归是____伟大构想的成功实践，开创了用和平方式解决历史遗留问题的新范例。&lt;br/&gt;&lt;br/&gt;答案：29；一国两制&lt;br/&gt;&lt;br/&gt;解析：依据：历史记录；《香港特别行政区基本法》序言。香港于1997年回归，2026年为回归29周年；一国两制由邓小平提出，在香港的成功实践为国际社会解决类似问题提供了重要借鉴。&lt;br/&gt;</t>
         </is>
       </c>
     </row>
